--- a/data/Designation_Master.xlsx
+++ b/data/Designation_Master.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://labournetservices-my.sharepoint.com/personal/praveen_sn_sambhavfoundation_org/Documents/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Praveen SN\PycharmProjects\website\mis_dashboard\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F628F75A-5919-4287-993C-F0064475E4AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C5CC582-D344-4C23-9C08-A55DD3EA4E7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{6A00FB05-938A-4025-B9E8-FF0B3E017A9E}"/>
   </bookViews>
@@ -39,10 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="53">
-  <si>
-    <t>Fitter - Construction</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="72">
   <si>
     <t>Designation</t>
   </si>
@@ -56,9 +53,6 @@
     <t>Warehouse &amp; Logistics</t>
   </si>
   <si>
-    <t>Foundation Skills for Stitching Operator</t>
-  </si>
-  <si>
     <t>Sales &amp; BD</t>
   </si>
   <si>
@@ -83,27 +77,18 @@
     <t>Cyber Security</t>
   </si>
   <si>
-    <t>Certificate Course in Tally - 2- I</t>
-  </si>
-  <si>
     <t>Domestic Data Entry Operator</t>
   </si>
   <si>
     <t>Assistant Data Analytics with Ai</t>
   </si>
   <si>
-    <t>Admin &amp; Office Support</t>
-  </si>
-  <si>
     <t>Guest Service Associate (Front Office)</t>
   </si>
   <si>
     <t>Accounts Executive (Accounts Payable and Receivables)</t>
   </si>
   <si>
-    <t>CNC / Machining</t>
-  </si>
-  <si>
     <t>Automotive Machining Operator</t>
   </si>
   <si>
@@ -131,9 +116,6 @@
     <t>Four Wheeler Service Technician</t>
   </si>
   <si>
-    <t>Tech - IT Hardware</t>
-  </si>
-  <si>
     <t>Tech - Household Appliances</t>
   </si>
   <si>
@@ -152,59 +134,134 @@
     <t>Tech - General</t>
   </si>
   <si>
-    <t>Hospitality - Front Office</t>
+    <t>Welder / Fabrication</t>
+  </si>
+  <si>
+    <t>Housekeeping</t>
+  </si>
+  <si>
+    <t>Management</t>
+  </si>
+  <si>
+    <t>Digital Marketing Manager</t>
+  </si>
+  <si>
+    <t>Warehouse Associate</t>
+  </si>
+  <si>
+    <t>General Duty Assistant</t>
+  </si>
+  <si>
+    <t>Life Skills for Success</t>
+  </si>
+  <si>
+    <t>Fitter - Fabrication</t>
+  </si>
+  <si>
+    <t>Retail Sales Associate</t>
+  </si>
+  <si>
+    <t>Sr. Associate - Desktop Publishing (DTP)</t>
+  </si>
+  <si>
+    <t>AutoCAD</t>
+  </si>
+  <si>
+    <t>Automotive Sales Consultant</t>
+  </si>
+  <si>
+    <t>Fitter- Electrical and Electronic Assembly</t>
+  </si>
+  <si>
+    <t>Automotive Assembly Operator</t>
+  </si>
+  <si>
+    <t>Automotive Body Painting Assistant</t>
+  </si>
+  <si>
+    <t>Automotive Plastic Moulding Technician</t>
+  </si>
+  <si>
+    <t>Automotive Welding Machine Assistant</t>
+  </si>
+  <si>
+    <t>Food &amp; Beverage Service - Associate</t>
+  </si>
+  <si>
+    <t>Two-Wheeler Internal Combustion Engine (ICE)</t>
+  </si>
+  <si>
+    <t>Domestic and Industrial Electrician</t>
+  </si>
+  <si>
+    <t>Construction Painter &amp; Decorator</t>
+  </si>
+  <si>
+    <t>Plumber - General</t>
+  </si>
+  <si>
+    <t>Auto Service Technician (2-wheelers)</t>
+  </si>
+  <si>
+    <t>HUL_Workplace Skills Course</t>
+  </si>
+  <si>
+    <t>Assistant Manual Metal Arc Welding/ Shielded Metal Arc Welding Welder</t>
+  </si>
+  <si>
+    <t>Front End Web Developer</t>
+  </si>
+  <si>
+    <t>Automotive Body Painting Technician</t>
+  </si>
+  <si>
+    <t>Automotive Assembly Technician</t>
+  </si>
+  <si>
+    <t>Assembly / Production</t>
+  </si>
+  <si>
+    <t>Engineering</t>
+  </si>
+  <si>
+    <t>Quality Control</t>
+  </si>
+  <si>
+    <t>Saksham 21st Century Skills</t>
+  </si>
+  <si>
+    <t>Digital Marketing With Ai</t>
   </si>
   <si>
     <t>Helper / General Labour</t>
   </si>
   <si>
+    <t>Maintenance &amp; EHS</t>
+  </si>
+  <si>
     <t>Plumber / Construction</t>
   </si>
   <si>
-    <t>Trainee / Apprentice</t>
-  </si>
-  <si>
-    <t>Machine Operator / Press</t>
-  </si>
-  <si>
-    <t>Welder / Fabrication</t>
-  </si>
-  <si>
     <t>Driver / Delivery</t>
   </si>
   <si>
-    <t>Housekeeping</t>
-  </si>
-  <si>
-    <t>Quality Control</t>
-  </si>
-  <si>
-    <t>Assembly / Production</t>
-  </si>
-  <si>
-    <t>Maintenance &amp; EHS</t>
-  </si>
-  <si>
-    <t>Engineering</t>
-  </si>
-  <si>
-    <t>Management</t>
+    <t>Tally - 2- I</t>
   </si>
   <si>
     <t>Tool Room &amp; Machining</t>
   </si>
   <si>
+    <t>F&amp;B / Kitchen Staff</t>
+  </si>
+  <si>
     <t>Healthcare / Pharma</t>
-  </si>
-  <si>
-    <t>F&amp;B / Kitchen Staff</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -218,13 +275,6 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -241,7 +291,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -262,24 +312,34 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -614,406 +674,739 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE83A65E-8AF8-457D-B5C9-68A58ACBE2A8}">
-  <dimension ref="A1:B55"/>
+  <dimension ref="A1:B91"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="23.3984375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="44.59765625" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="44.59765625" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="4" t="s">
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A2" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A3" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="4" t="s">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A4" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A5" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A6" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A7" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A3" s="1" t="s">
+      <c r="B8" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A9" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A10" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A11" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A12" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A13" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A14" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A15" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A16" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A17" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A18" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A19" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A20" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A21" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A22" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A23" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A24" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A25" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A26" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A27" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A28" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A29" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A30" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B30" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A31" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B32" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A4" s="1" t="s">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A34" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A35" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A36" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A37" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A38" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A39" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A40" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A41" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A42" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A43" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A44" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A45" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A46" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A47" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A48" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A49" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A50" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A51" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A52" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A53" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A54" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A55" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A56" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A57" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A58" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A59" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A60" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A61" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A62" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A63" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A64" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A65" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A66" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A67" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A68" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A69" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A70" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A71" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A72" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A73" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A74" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A75" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A76" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A77" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A78" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A79" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A80" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A81" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A82" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B82" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A83" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B83" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A8" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" s="4" t="s">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A84" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B84" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A9" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A10" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A11" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A12" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A13" s="1" t="s">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A85" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B13" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A14" s="1" t="s">
+      <c r="B85" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A86" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A15" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A16" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B16" s="3" t="s">
+      <c r="B86" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A87" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B87" s="3" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A17" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A18" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A19" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A20" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A21" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A22" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A23" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B23" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A24" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B24" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A25" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A26" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B26" s="4" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A27" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B27" s="4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A28" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B28" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A29" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B29" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A30" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B30" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A31" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B31" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A32" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B32" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A33" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B33" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A34" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A35" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B35" s="4" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A36" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B36" s="4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A37" s="1" t="s">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A88" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B88" s="3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A89" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B89" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A90" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B90" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A91" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B91" s="3" t="s">
         <v>36</v>
-      </c>
-      <c r="B37" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A38" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B38" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A39" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B39" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A40" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B40" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A41" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A42" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A43" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A44" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A45" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A46" s="1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A47" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A48" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A49" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A50" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A51" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A52" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A53" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A54" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A55" s="1" t="s">
-        <v>52</v>
       </c>
     </row>
   </sheetData>
